--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:15</t>
+    <t xml:space="preserve">2026-09-09 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:10</t>
+    <t xml:space="preserve">2026-09-17 14:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:06</t>
+    <t xml:space="preserve">2026-09-23 12:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:35</t>
+    <t xml:space="preserve">2026-10-02 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:03</t>
+    <t xml:space="preserve">2026-10-05 10:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
